--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487454_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487454_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5316</v>
+        <v>6.8341</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0426</v>
+        <v>6.1847</v>
       </c>
       <c r="F2" t="n">
-        <v>0.489</v>
+        <v>0.6494</v>
       </c>
       <c r="G2" t="n">
         <v>5.3681</v>
@@ -610,13 +610,13 @@
         <v>2.546</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0858</v>
+        <v>0.2167</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7546</v>
+        <v>0.3876</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3312</v>
+        <v>-0.1708</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1217</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9211</v>
+        <v>5.8808</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2672</v>
+        <v>4.3071</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6539</v>
+        <v>1.5737</v>
       </c>
       <c r="G3" t="n">
         <v>1.7577</v>
@@ -688,13 +688,13 @@
         <v>2.546</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4034</v>
+        <v>0.5562</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1286</v>
+        <v>-0.0888</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7252</v>
+        <v>0.645</v>
       </c>
       <c r="V3" t="n">
         <v>1.2166</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. HOGAN</t>
+          <t>K. VAN WIJK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7743</v>
+        <v>4.5727</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0934</v>
+        <v>2.6242</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3191</v>
+        <v>1.9486</v>
       </c>
       <c r="G4" t="n">
-        <v>1.808</v>
+        <v>-0.6123</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9993</v>
+        <v>1.5805</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8087</v>
+        <v>-2.1928</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0674</v>
+        <v>1.1356</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9254</v>
+        <v>2.2575</v>
       </c>
       <c r="L4" t="n">
-        <v>2.142</v>
+        <v>-1.122</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2594</v>
+        <v>-1.7479</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07389999999999999</v>
+        <v>-0.677</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3333</v>
+        <v>-1.0708</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7626</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.1336</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7626</v>
+        <v>2.7419</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4832</v>
+        <v>0.7103</v>
       </c>
       <c r="T4" t="n">
-        <v>3.0836</v>
+        <v>0.4217</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3996</v>
+        <v>0.2886</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.2795</v>
+        <v>4.8664</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0576</v>
+        <v>4.2005</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.2219</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. VAN WIJK</t>
+          <t>D. HOGAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.7342</v>
+        <v>2.6115</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8124</v>
+        <v>4.2513</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9218</v>
+        <v>-1.6398</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6123</v>
+        <v>1.808</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5805</v>
+        <v>0.9993</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.1928</v>
+        <v>0.8087</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1356</v>
+        <v>3.0674</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2575</v>
+        <v>0.9254</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.122</v>
+        <v>2.142</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7479</v>
+        <v>-1.2594</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.677</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0708</v>
+        <v>-1.3333</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3917</v>
+        <v>1.7626</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.1336</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7419</v>
+        <v>1.7626</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8718</v>
+        <v>1.3204</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6099</v>
+        <v>1.2415</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2619</v>
+        <v>0.0788</v>
       </c>
       <c r="V5" t="n">
-        <v>4.8664</v>
+        <v>-2.2795</v>
       </c>
       <c r="W5" t="n">
-        <v>4.2005</v>
+        <v>-0.0576</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6659</v>
+        <v>-2.2219</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0311</v>
+        <v>2.0833</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2332</v>
+        <v>2.3122</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2021</v>
+        <v>-0.2289</v>
       </c>
       <c r="G6" t="n">
         <v>1.5888</v>
@@ -922,13 +922,13 @@
         <v>0.9792</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5425</v>
+        <v>0.5948</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5121</v>
+        <v>0.5911</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0304</v>
+        <v>0.0037</v>
       </c>
       <c r="V6" t="n">
         <v>-0.8837</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1923</v>
+        <v>0.3305</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9741</v>
+        <v>0.8717</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7818000000000001</v>
+        <v>-0.5412</v>
       </c>
       <c r="G7" t="n">
         <v>0.3172</v>
@@ -1000,13 +1000,13 @@
         <v>1.3709</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2133</v>
+        <v>0.3516</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0288</v>
+        <v>-0.0735</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1845</v>
+        <v>0.4251</v>
       </c>
       <c r="V7" t="n">
         <v>-0.73</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1146</v>
+        <v>-0.0611</v>
       </c>
       <c r="E8" t="n">
         <v>-0.019</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0956</v>
+        <v>-0.0422</v>
       </c>
       <c r="G8" t="n">
         <v>-0.09080000000000001</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0238</v>
+        <v>0.0297</v>
       </c>
       <c r="T8" t="n">
         <v>-0.0594</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0356</v>
+        <v>0.0891</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. REY PEREZ</t>
+          <t>M. OLOWOKERE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3655</v>
+        <v>-0.542</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3074</v>
+        <v>-2.5782</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9419</v>
+        <v>2.0362</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4179</v>
+        <v>-5.2675</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2066</v>
+        <v>-1.1089</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7887</v>
+        <v>-4.1587</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2065</v>
+        <v>-3.3999</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0003</v>
+        <v>-0.8421999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7938</v>
+        <v>-2.5576</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2114</v>
+        <v>-1.8677</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2062</v>
+        <v>-0.2667</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0052</v>
+        <v>-1.601</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9792</v>
+        <v>1.7626</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9792</v>
+        <v>3.7211</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1958</v>
+        <v>0.6514</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4446</v>
+        <v>0.347</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2488</v>
+        <v>0.3044</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2.3115</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.4332</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.1217</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. PULLEIRO GONZALEZ</t>
+          <t>M. SOUTO PARRADO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7925</v>
+        <v>-0.6318</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4241</v>
+        <v>-2.7633</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2166</v>
+        <v>2.1315</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.8799</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0612</v>
+        <v>-1.8146</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8083</v>
+        <v>0.9347</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3471</v>
+        <v>-0.8371</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3471</v>
+        <v>-2.2969</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.4598</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2166</v>
+        <v>-0.0428</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4083</v>
+        <v>0.4822</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8083</v>
+        <v>-0.525</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.3709</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.1543</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.5253</v>
       </c>
       <c r="S10" t="n">
-        <v>0.077</v>
+        <v>0.4908</v>
       </c>
       <c r="T10" t="n">
-        <v>0.077</v>
+        <v>0.2282</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.2626</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.6136</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.6136</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. OLOWOKERE</t>
+          <t>H. REY PEREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1098</v>
+        <v>-0.6725</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4133</v>
+        <v>-1.6144</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3035</v>
+        <v>0.9419</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.2675</v>
+        <v>0.4179</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1089</v>
+        <v>1.2066</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.1587</v>
+        <v>-0.7887</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.3999</v>
+        <v>0.2065</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8421999999999999</v>
+        <v>1.0003</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.5576</v>
+        <v>-0.7938</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8677</v>
+        <v>0.2114</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2667</v>
+        <v>0.2062</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.601</v>
+        <v>0.0052</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7626</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R11" t="n">
-        <v>3.7211</v>
+        <v>0.9792</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0835</v>
+        <v>-0.1112</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4882</v>
+        <v>0.1376</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5717</v>
+        <v>-0.2488</v>
       </c>
       <c r="V11" t="n">
-        <v>2.3115</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.4332</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. SOUTO PARRADO</t>
+          <t>R. PULLEIRO GONZALEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6273</v>
+        <v>-0.7925</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5984</v>
+        <v>0.4241</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9711</v>
+        <v>-1.2166</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8799</v>
+        <v>-0.8695000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.8146</v>
+        <v>-0.0612</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9347</v>
+        <v>-0.8083</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8371</v>
+        <v>0.3471</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.2969</v>
+        <v>0.3471</v>
       </c>
       <c r="L12" t="n">
-        <v>1.4598</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0428</v>
+        <v>-1.2166</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4822</v>
+        <v>-0.4083</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.525</v>
+        <v>-0.8083</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3709</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1543</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.5253</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5047</v>
+        <v>0.077</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.607</v>
+        <v>0.077</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1022</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.6136</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.6136</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.6603</v>
+        <v>-3.5045</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.719</v>
+        <v>-1.6167</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9413</v>
+        <v>-1.8878</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8918</v>
@@ -1468,13 +1468,13 @@
         <v>0.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3561</v>
+        <v>-0.2003</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1188</v>
+        <v>-0.0165</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2373</v>
+        <v>-0.1838</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8249</v>
@@ -1501,31 +1501,31 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>15.5146</v>
+        <v>16.1085</v>
       </c>
       <c r="E14" t="n">
-        <v>11.7899</v>
+        <v>12.3837</v>
       </c>
       <c r="F14" t="n">
-        <v>3.7247</v>
+        <v>3.724800000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6459</v>
+        <v>2.645900000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>4.088199999999999</v>
+        <v>4.0882</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.442400000000001</v>
+        <v>-1.4424</v>
       </c>
       <c r="J14" t="n">
         <v>12.9689</v>
       </c>
       <c r="K14" t="n">
-        <v>5.749499999999999</v>
+        <v>5.749500000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>7.219100000000001</v>
+        <v>7.219100000000002</v>
       </c>
       <c r="M14" t="n">
         <v>-10.323</v>
@@ -1546,13 +1546,13 @@
         <v>20.5639</v>
       </c>
       <c r="S14" t="n">
-        <v>4.0933</v>
+        <v>4.687399999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>2.599400000000001</v>
+        <v>3.1935</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4938</v>
+        <v>1.4939</v>
       </c>
       <c r="V14" t="n">
         <v>0.9411</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.6734</v>
+        <v>5.3737</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4262</v>
+        <v>5.0169</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2471</v>
+        <v>0.3569</v>
       </c>
       <c r="G15" t="n">
         <v>2.8265</v>
@@ -1624,13 +1624,13 @@
         <v>1.3709</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0416</v>
+        <v>-0.258</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3129</v>
+        <v>-0.0965</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2713</v>
+        <v>-0.1616</v>
       </c>
       <c r="V15" t="n">
         <v>1.4344</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6806</v>
+        <v>0.3939</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0703</v>
+        <v>1.968</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3898</v>
+        <v>-1.5741</v>
       </c>
       <c r="G16" t="n">
         <v>0.745</v>
@@ -1702,13 +1702,13 @@
         <v>1.7626</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1314</v>
+        <v>-0.1553</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1317</v>
+        <v>-0.2341</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2631</v>
+        <v>0.0788</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2999</v>
+        <v>-0.3049</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1073</v>
+        <v>-0.7114</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1926</v>
+        <v>0.4065</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2632</v>
@@ -1780,13 +1780,13 @@
         <v>0.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7589</v>
+        <v>0.1541</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0257</v>
+        <v>0.207</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2668</v>
+        <v>-0.0529</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ TAPIA</t>
+          <t>Y. PINAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2473</v>
+        <v>-1.329</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6643</v>
+        <v>-1.269</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.583</v>
+        <v>-0.0599</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.5475</v>
+        <v>0.5591</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0183</v>
+        <v>-0.0323</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5658</v>
+        <v>0.5914</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5703</v>
+        <v>0.1425</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0546</v>
+        <v>0.1021</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5158</v>
+        <v>0.0404</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9771</v>
+        <v>0.4166</v>
       </c>
       <c r="N18" t="n">
-        <v>0.07290000000000001</v>
+        <v>-0.1344</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0501</v>
+        <v>0.551</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9585</v>
+        <v>0.1958</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9585</v>
+        <v>1.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4995</v>
+        <v>-0.592</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3694</v>
+        <v>-0.4323</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8689</v>
+        <v>-0.1597</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.1578</v>
+        <v>-1.492</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.4332</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Y. PINAS</t>
+          <t>M. RODRÍGUEZ BLANCO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5917</v>
+        <v>-1.4991</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3714</v>
+        <v>1.2629</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2203</v>
+        <v>-2.7619</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5591</v>
+        <v>0.3743</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0323</v>
+        <v>0.8285</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5914</v>
+        <v>-0.4542</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1425</v>
+        <v>2.7283</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1021</v>
+        <v>2.5263</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0404</v>
+        <v>0.2021</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4166</v>
+        <v>-2.3541</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1344</v>
+        <v>-1.6978</v>
       </c>
       <c r="O19" t="n">
-        <v>0.551</v>
+        <v>-0.6563</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1958</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1751</v>
+        <v>1.5668</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8547</v>
+        <v>-0.598</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5346</v>
+        <v>-0.1153</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3201</v>
+        <v>-0.4827</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.492</v>
+        <v>-0.8837</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.6083</v>
       </c>
       <c r="X19" t="n">
         <v>-1.492</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. RODRÍGUEZ BLANCO</t>
+          <t>S. RODRÍGUEZ TAPIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6908</v>
+        <v>-1.6188</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3652</v>
+        <v>-0.6643</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.056</v>
+        <v>-0.9544</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3743</v>
+        <v>-1.5475</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8285</v>
+        <v>0.0183</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4542</v>
+        <v>-1.5658</v>
       </c>
       <c r="J20" t="n">
-        <v>2.7283</v>
+        <v>-0.5703</v>
       </c>
       <c r="K20" t="n">
-        <v>2.5263</v>
+        <v>-0.0546</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2021</v>
+        <v>-0.5158</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3541</v>
+        <v>-0.9771</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.6978</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6563</v>
+        <v>-1.0501</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3917</v>
+        <v>1.9585</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5668</v>
+        <v>1.9585</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7897</v>
+        <v>0.1281</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0129</v>
+        <v>-0.3694</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7766999999999999</v>
+        <v>0.4974</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8837</v>
+        <v>-2.1578</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6083</v>
+        <v>0.2754</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.492</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9077</v>
+        <v>-1.9879</v>
       </c>
       <c r="E21" t="n">
         <v>-1.6586</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2491</v>
+        <v>-0.3293</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0949</v>
@@ -2092,13 +2092,13 @@
         <v>0.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2252</v>
+        <v>-0.3054</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1188</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1064</v>
+        <v>-0.1866</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0775</v>
+        <v>-2.6635</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4613</v>
+        <v>-2.1543</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6161</v>
+        <v>-0.5092</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7005</v>
@@ -2170,13 +2170,13 @@
         <v>0.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0268</v>
+        <v>-0.6128</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4158</v>
+        <v>-0.1088</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.611</v>
+        <v>-0.504</v>
       </c>
       <c r="V22" t="n">
         <v>1.2166</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Q. HUANG</t>
+          <t>N. FUENTES PRADO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5197</v>
+        <v>-2.7239</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9467</v>
+        <v>-3.5685</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.4664</v>
+        <v>0.8446</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3689</v>
+        <v>-0.6596</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2525</v>
+        <v>-0.8928</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6214</v>
+        <v>0.2332</v>
       </c>
       <c r="J23" t="n">
-        <v>2.2647</v>
+        <v>0.7883</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9714</v>
+        <v>-0.6262</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2933</v>
+        <v>1.4145</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8957</v>
+        <v>-1.448</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2239</v>
+        <v>-0.2667</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-1.1813</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.9585</v>
+        <v>-3.7211</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9585</v>
+        <v>-5.8755</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.1543</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1125</v>
+        <v>-0.4435</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6405</v>
+        <v>-0.5817</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.528</v>
+        <v>0.1382</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.0427</v>
+        <v>2.1003</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.1003</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.0427</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N. FUENTES PRADO</t>
+          <t>Q. HUANG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.5859</v>
+        <v>-3.6977</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.0802</v>
+        <v>0.742</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4943</v>
+        <v>-4.4396</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6596</v>
+        <v>0.3689</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8928</v>
+        <v>-0.2525</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2332</v>
+        <v>0.6214</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7883</v>
+        <v>2.2647</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6262</v>
+        <v>0.9714</v>
       </c>
       <c r="L24" t="n">
-        <v>1.4145</v>
+        <v>1.2933</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.448</v>
+        <v>-1.8957</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2667</v>
+        <v>-1.2239</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.1813</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.7211</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.8755</v>
+        <v>-1.9585</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1543</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3054</v>
+        <v>-0.0654</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0933</v>
+        <v>0.4358</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2121</v>
+        <v>-0.5012</v>
       </c>
       <c r="V24" t="n">
-        <v>2.1003</v>
+        <v>-2.0427</v>
       </c>
       <c r="W24" t="n">
-        <v>2.1003</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-2.0427</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5478</v>
+        <v>-4.7752</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.4045</v>
+        <v>-2.6882</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.1432</v>
+        <v>-2.087</v>
       </c>
       <c r="G25" t="n">
         <v>-2.254</v>
@@ -2404,13 +2404,13 @@
         <v>1.1751</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4356</v>
+        <v>-0.663</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7963</v>
+        <v>-0.08</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6392</v>
+        <v>-0.583</v>
       </c>
       <c r="V25" t="n">
         <v>0.8837</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-15.5145</v>
+        <v>-14.8324</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.724600000000001</v>
+        <v>-3.7245</v>
       </c>
       <c r="F26" t="n">
-        <v>-11.7899</v>
+        <v>-11.1074</v>
       </c>
       <c r="G26" t="n">
         <v>-2.6459</v>
@@ -2452,7 +2452,7 @@
         <v>-4.0881</v>
       </c>
       <c r="I26" t="n">
-        <v>1.442299999999999</v>
+        <v>1.4423</v>
       </c>
       <c r="J26" t="n">
         <v>10.3228</v>
@@ -2470,7 +2470,7 @@
         <v>-5.7497</v>
       </c>
       <c r="O26" t="n">
-        <v>-7.219100000000001</v>
+        <v>-7.2191</v>
       </c>
       <c r="P26" t="n">
         <v>-7.8339</v>
@@ -2482,13 +2482,13 @@
         <v>12.7301</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.0935</v>
+        <v>-3.4112</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.4937</v>
+        <v>-1.4941</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.5996</v>
+        <v>-1.9173</v>
       </c>
       <c r="V26" t="n">
         <v>-0.9412000000000004</v>
@@ -2497,7 +2497,7 @@
         <v>8.0106</v>
       </c>
       <c r="X26" t="n">
-        <v>-8.951899999999998</v>
+        <v>-8.9519</v>
       </c>
     </row>
   </sheetData>
